--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9753,0.0060,0.0131,0.0002</t>
-  </si>
-  <si>
-    <t>0.9316,0.0253,0.0194,0.0013</t>
-  </si>
-  <si>
-    <t>0.9636,0.0134,0.0108,0.0003</t>
-  </si>
-  <si>
-    <t>0.8961,0.0232,0.0208,0.0064</t>
-  </si>
-  <si>
-    <t>0.8817,0.0360,0.0191,0.0078</t>
-  </si>
-  <si>
-    <t>0.8435,0.0436,0.0406,0.0111</t>
-  </si>
-  <si>
-    <t>0.7911,0.0476,0.0453,0.0230</t>
-  </si>
-  <si>
-    <t>0.8065,0.0433,0.0253,0.0237</t>
-  </si>
-  <si>
-    <t>0.8305,0.1440,0.0191,0.0030</t>
-  </si>
-  <si>
-    <t>0.7552,0.1068,0.0536,0.0105</t>
-  </si>
-  <si>
-    <t>0.9279,0.0215,0.0084,0.0053</t>
-  </si>
-  <si>
-    <t>0.8339,0.0596,0.0258,0.0110</t>
-  </si>
-  <si>
-    <t>0.9714,0.0124,0.0085,0.0001</t>
-  </si>
-  <si>
-    <t>0.9665,0.0083,0.0179,0.0001</t>
-  </si>
-  <si>
-    <t>0.9614,0.0057,0.0276,0.0001</t>
-  </si>
-  <si>
-    <t>0.9631,0.0041,0.0348,0.0001</t>
-  </si>
-  <si>
-    <t>0.9162,0.0474,0.0296,0.0003</t>
-  </si>
-  <si>
-    <t>0.1749,0.8936,0.0584,0.0003</t>
-  </si>
-  <si>
-    <t>0.3062,0.7426,0.1275,0.0022</t>
-  </si>
-  <si>
-    <t>0.8162,0.1547,0.0373,0.0012</t>
-  </si>
-  <si>
-    <t>0.2262,0.8086,0.0965,0.0019</t>
-  </si>
-  <si>
-    <t>0.1291,0.9101,0.0670,0.0010</t>
-  </si>
-  <si>
-    <t>0.9461,0.0020,0.0616,0.0001</t>
-  </si>
-  <si>
-    <t>0.9698,0.0016,0.0327,0.0001</t>
-  </si>
-  <si>
-    <t>0.9137,0.0044,0.1159,0.0001</t>
-  </si>
-  <si>
-    <t>0.6884,0.1489,0.0947,0.0004</t>
-  </si>
-  <si>
-    <t>0.9555,0.0044,0.0373,0.0001</t>
-  </si>
-  <si>
-    <t>0.9422,0.0024,0.0790,0.0001</t>
-  </si>
-  <si>
-    <t>0.5074,0.0143,0.5928,0.0005</t>
-  </si>
-  <si>
-    <t>0.8422,0.0939,0.0581,0.0018</t>
-  </si>
-  <si>
-    <t>0.8111,0.1048,0.0519,0.0031</t>
-  </si>
-  <si>
-    <t>0.0927,0.1327,0.9190,0.0035</t>
-  </si>
-  <si>
-    <t>0.9016,0.0360,0.0518,0.0010</t>
-  </si>
-  <si>
-    <t>0.7890,0.1222,0.0572,0.0035</t>
-  </si>
-  <si>
-    <t>0.7461,0.1579,0.0716,0.0065</t>
-  </si>
-  <si>
-    <t>0.8056,0.1418,0.0669,0.0028</t>
-  </si>
-  <si>
-    <t>0.9556,0.0267,0.0150,0.0004</t>
-  </si>
-  <si>
-    <t>0.8340,0.0743,0.0337,0.0006</t>
-  </si>
-  <si>
-    <t>0.9673,0.0016,0.0282,0.0001</t>
-  </si>
-  <si>
-    <t>0.9606,0.0038,0.0352,0.0001</t>
-  </si>
-  <si>
-    <t>0.9766,0.0014,0.0192,0.0001</t>
-  </si>
-  <si>
-    <t>0.9865,0.0015,0.0127,0.0000</t>
-  </si>
-  <si>
-    <t>0.1456,0.8141,0.0834,0.0006</t>
-  </si>
-  <si>
-    <t>0.8585,0.0183,0.1543,0.0004</t>
-  </si>
-  <si>
-    <t>0.8858,0.0928,0.0263,0.0007</t>
-  </si>
-  <si>
-    <t>0.6056,0.5437,0.0321,0.0001</t>
-  </si>
-  <si>
-    <t>0.1042,0.9344,0.0229,0.0003</t>
-  </si>
-  <si>
-    <t>0.7088,0.2964,0.0341,0.0018</t>
-  </si>
-  <si>
-    <t>0.3686,0.1462,0.5051,0.0017</t>
-  </si>
-  <si>
-    <t>0.7060,0.0039,0.5345,0.0001</t>
-  </si>
-  <si>
-    <t>0.9220,0.0111,0.0817,0.0002</t>
-  </si>
-  <si>
-    <t>0.9140,0.0022,0.1512,0.0000</t>
-  </si>
-  <si>
-    <t>0.5126,0.0370,0.5918,0.0005</t>
-  </si>
-  <si>
-    <t>0.7904,0.0334,0.1393,0.0001</t>
-  </si>
-  <si>
-    <t>0.8878,0.0702,0.0299,0.0016</t>
-  </si>
-  <si>
-    <t>0.8081,0.1478,0.0651,0.0043</t>
-  </si>
-  <si>
-    <t>0.7894,0.0963,0.0403,0.0099</t>
-  </si>
-  <si>
-    <t>0.4111,0.3958,0.3625,0.0048</t>
-  </si>
-  <si>
-    <t>0.8571,0.0537,0.0353,0.0066</t>
-  </si>
-  <si>
-    <t>0.8123,0.0444,0.0462,0.0263</t>
-  </si>
-  <si>
-    <t>0.6792,0.2077,0.1061,0.0078</t>
-  </si>
-  <si>
-    <t>0.2302,0.0834,0.7172,0.0002</t>
-  </si>
-  <si>
-    <t>0.8527,0.0056,0.1892,0.0002</t>
-  </si>
-  <si>
-    <t>0.9527,0.0021,0.0621,0.0001</t>
-  </si>
-  <si>
-    <t>0.2614,0.3601,0.4074,0.0001</t>
-  </si>
-  <si>
-    <t>0.7423,0.0016,0.4862,0.0000</t>
-  </si>
-  <si>
-    <t>0.8313,0.2760,0.0093,0.0002</t>
-  </si>
-  <si>
-    <t>0.0862,0.9485,0.0108,0.0002</t>
-  </si>
-  <si>
-    <t>0.9334,0.0475,0.0148,0.0005</t>
-  </si>
-  <si>
-    <t>0.8442,0.1343,0.0495,0.0005</t>
-  </si>
-  <si>
-    <t>0.4975,0.1138,0.5055,0.0023</t>
-  </si>
-  <si>
-    <t>0.9019,0.0203,0.0534,0.0001</t>
-  </si>
-  <si>
-    <t>0.8220,0.0153,0.2058,0.0002</t>
-  </si>
-  <si>
-    <t>0.3541,0.6340,0.0322,0.0001</t>
-  </si>
-  <si>
-    <t>0.0651,0.6964,0.3772,0.0002</t>
-  </si>
-  <si>
-    <t>0.9542,0.0096,0.0207,0.0008</t>
-  </si>
-  <si>
-    <t>0.7656,0.1510,0.0732,0.0038</t>
-  </si>
-  <si>
-    <t>0.9456,0.0249,0.0170,0.0004</t>
-  </si>
-  <si>
-    <t>0.9474,0.0258,0.0125,0.0006</t>
-  </si>
-  <si>
-    <t>0.8788,0.0354,0.0538,0.0033</t>
-  </si>
-  <si>
-    <t>0.9807,0.0085,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9052,0.0078,0.0879,0.0001</t>
-  </si>
-  <si>
-    <t>0.7337,0.0281,0.2954,0.0002</t>
-  </si>
-  <si>
-    <t>0.7658,0.1130,0.0482,0.0001</t>
-  </si>
-  <si>
-    <t>0.7107,0.0131,0.2998,0.0001</t>
-  </si>
-  <si>
-    <t>0.8568,0.0148,0.1614,0.0001</t>
-  </si>
-  <si>
-    <t>0.9335,0.0248,0.0221,0.0001</t>
-  </si>
-  <si>
-    <t>0.7113,0.1312,0.0433,0.0170</t>
-  </si>
-  <si>
-    <t>0.7941,0.0782,0.0513,0.0080</t>
-  </si>
-  <si>
-    <t>0.7755,0.0808,0.0432,0.0090</t>
-  </si>
-  <si>
-    <t>0.8378,0.0670,0.0483,0.0057</t>
-  </si>
-  <si>
-    <t>0.8621,0.0385,0.0336,0.0050</t>
-  </si>
-  <si>
-    <t>0.8030,0.0263,0.0383,0.0332</t>
-  </si>
-  <si>
-    <t>0.7305,0.1050,0.0592,0.0160</t>
-  </si>
-  <si>
-    <t>0.8673,0.0638,0.0349,0.0036</t>
-  </si>
-  <si>
-    <t>0.8347,0.0228,0.0196,0.0270</t>
-  </si>
-  <si>
-    <t>0.8132,0.0252,0.0315,0.0289</t>
-  </si>
-  <si>
-    <t>0.7773,0.1271,0.0507,0.0086</t>
-  </si>
-  <si>
-    <t>0.8415,0.0780,0.0352,0.0071</t>
-  </si>
-  <si>
-    <t>0.8017,0.0814,0.0671,0.0066</t>
-  </si>
-  <si>
-    <t>0.7969,0.1019,0.0470,0.0074</t>
-  </si>
-  <si>
-    <t>0.8094,0.0597,0.0516,0.0127</t>
-  </si>
-  <si>
-    <t>0.8693,0.0668,0.0191,0.0024</t>
-  </si>
-  <si>
-    <t>0.2870,0.0185,0.8798,0.0003</t>
-  </si>
-  <si>
-    <t>0.9343,0.0078,0.0479,0.0002</t>
-  </si>
-  <si>
-    <t>0.9625,0.0054,0.0310,0.0001</t>
-  </si>
-  <si>
-    <t>0.9287,0.0066,0.0526,0.0003</t>
-  </si>
-  <si>
-    <t>0.6900,0.2881,0.0791,0.0018</t>
-  </si>
-  <si>
-    <t>0.6493,0.2783,0.1404,0.0026</t>
-  </si>
-  <si>
-    <t>0.7419,0.2436,0.0830,0.0027</t>
-  </si>
-  <si>
-    <t>0.3747,0.7045,0.0794,0.0038</t>
-  </si>
-  <si>
-    <t>0.5189,0.5105,0.1229,0.0030</t>
-  </si>
-  <si>
-    <t>0.0408,0.9657,0.0312,0.0020</t>
-  </si>
-  <si>
-    <t>0.7197,0.1944,0.0877,0.0066</t>
-  </si>
-  <si>
-    <t>0.9100,0.0455,0.0282,0.0013</t>
-  </si>
-  <si>
-    <t>0.9390,0.0080,0.0544,0.0002</t>
-  </si>
-  <si>
-    <t>0.9421,0.0135,0.0376,0.0004</t>
-  </si>
-  <si>
-    <t>0.9431,0.0174,0.0318,0.0004</t>
-  </si>
-  <si>
-    <t>0.9079,0.0471,0.0431,0.0005</t>
-  </si>
-  <si>
-    <t>0.3700,0.8254,0.0115,0.0001</t>
-  </si>
-  <si>
-    <t>0.6106,0.5195,0.0287,0.0008</t>
-  </si>
-  <si>
-    <t>0.7157,0.3195,0.0654,0.0003</t>
-  </si>
-  <si>
-    <t>0.1406,0.7568,0.3269,0.0010</t>
-  </si>
-  <si>
-    <t>0.8675,0.1569,0.0186,0.0004</t>
-  </si>
-  <si>
-    <t>0.9395,0.0280,0.0169,0.0008</t>
-  </si>
-  <si>
-    <t>0.6917,0.2087,0.1056,0.0059</t>
-  </si>
-  <si>
-    <t>0.8592,0.0513,0.0367,0.0070</t>
-  </si>
-  <si>
-    <t>0.8693,0.0544,0.0248,0.0051</t>
-  </si>
-  <si>
-    <t>0.8493,0.0529,0.0564,0.0038</t>
-  </si>
-  <si>
-    <t>0.7871,0.0452,0.0453,0.0216</t>
-  </si>
-  <si>
-    <t>0.8827,0.0446,0.0193,0.0063</t>
-  </si>
-  <si>
-    <t>0.8934,0.0438,0.0383,0.0020</t>
-  </si>
-  <si>
-    <t>0.7650,0.1008,0.0456,0.0107</t>
-  </si>
-  <si>
-    <t>0.7181,0.1126,0.0751,0.0188</t>
-  </si>
-  <si>
-    <t>0.9410,0.0030,0.0748,0.0000</t>
-  </si>
-  <si>
-    <t>0.8489,0.0503,0.0492,0.0001</t>
-  </si>
-  <si>
-    <t>0.5868,0.0195,0.4214,0.0001</t>
-  </si>
-  <si>
-    <t>0.9726,0.0011,0.0255,0.0001</t>
-  </si>
-  <si>
-    <t>0.9693,0.0079,0.0164,0.0000</t>
-  </si>
-  <si>
-    <t>0.9321,0.0251,0.0338,0.0004</t>
-  </si>
-  <si>
-    <t>0.9568,0.0064,0.0416,0.0001</t>
-  </si>
-  <si>
-    <t>0.8997,0.0162,0.0974,0.0006</t>
-  </si>
-  <si>
-    <t>0.9509,0.0097,0.0176,0.0011</t>
-  </si>
-  <si>
-    <t>0.9379,0.0282,0.0183,0.0010</t>
-  </si>
-  <si>
-    <t>0.9716,0.0041,0.0128,0.0004</t>
-  </si>
-  <si>
-    <t>0.7988,0.0732,0.0596,0.0078</t>
-  </si>
-  <si>
-    <t>0.6587,0.0318,0.4089,0.0005</t>
-  </si>
-  <si>
-    <t>0.8419,0.0562,0.0388,0.0071</t>
-  </si>
-  <si>
-    <t>0.8159,0.1282,0.0267,0.0024</t>
-  </si>
-  <si>
-    <t>0.8812,0.0360,0.0297,0.0048</t>
-  </si>
-  <si>
-    <t>0.7039,0.2632,0.0708,0.0049</t>
-  </si>
-  <si>
-    <t>0.8929,0.0696,0.0254,0.0013</t>
-  </si>
-  <si>
-    <t>0.7439,0.1488,0.1161,0.0048</t>
-  </si>
-  <si>
-    <t>0.8723,0.0493,0.0355,0.0036</t>
-  </si>
-  <si>
-    <t>0.2983,0.1942,0.6706,0.0115</t>
-  </si>
-  <si>
-    <t>0.8054,0.1087,0.0220,0.0077</t>
-  </si>
-  <si>
-    <t>0.8915,0.0434,0.0323,0.0013</t>
-  </si>
-  <si>
-    <t>0.6341,0.2854,0.1648,0.0018</t>
-  </si>
-  <si>
-    <t>0.9164,0.0508,0.0190,0.0009</t>
-  </si>
-  <si>
-    <t>0.9295,0.0253,0.0295,0.0006</t>
-  </si>
-  <si>
-    <t>0.7352,0.2272,0.0609,0.0053</t>
-  </si>
-  <si>
-    <t>0.9269,0.0306,0.0319,0.0008</t>
-  </si>
-  <si>
-    <t>0.7998,0.1975,0.0524,0.0006</t>
-  </si>
-  <si>
-    <t>0.8902,0.0440,0.0278,0.0035</t>
-  </si>
-  <si>
-    <t>0.6036,0.1194,0.0754,0.0434</t>
-  </si>
-  <si>
-    <t>0.7866,0.0887,0.0520,0.0098</t>
-  </si>
-  <si>
-    <t>0.9052,0.0181,0.0120,0.0087</t>
-  </si>
-  <si>
-    <t>0.8642,0.0375,0.0324,0.0086</t>
-  </si>
-  <si>
-    <t>0.7852,0.1390,0.0505,0.0068</t>
-  </si>
-  <si>
-    <t>0.8807,0.0290,0.0255,0.0087</t>
-  </si>
-  <si>
-    <t>0.8311,0.0648,0.0229,0.0073</t>
-  </si>
-  <si>
-    <t>0.7994,0.1464,0.0649,0.0015</t>
-  </si>
-  <si>
-    <t>0.7507,0.1900,0.0850,0.0022</t>
-  </si>
-  <si>
-    <t>0.8557,0.0784,0.0503,0.0031</t>
-  </si>
-  <si>
-    <t>0.9105,0.0373,0.0067,0.0017</t>
-  </si>
-  <si>
-    <t>0.6972,0.1024,0.0419,0.0200</t>
-  </si>
-  <si>
-    <t>0.8829,0.0372,0.0319,0.0039</t>
-  </si>
-  <si>
-    <t>0.7459,0.1749,0.0684,0.0038</t>
-  </si>
-  <si>
-    <t>0.7285,0.2446,0.0577,0.0030</t>
-  </si>
-  <si>
-    <t>0.2157,0.0574,0.8861,0.0005</t>
-  </si>
-  <si>
-    <t>0.7315,0.2372,0.0349,0.0040</t>
-  </si>
-  <si>
-    <t>0.8142,0.0093,0.2550,0.0001</t>
-  </si>
-  <si>
-    <t>0.9654,0.0020,0.0334,0.0001</t>
-  </si>
-  <si>
-    <t>0.9107,0.0107,0.0837,0.0001</t>
-  </si>
-  <si>
-    <t>0.5702,0.0965,0.2167,0.0003</t>
-  </si>
-  <si>
-    <t>0.9707,0.0012,0.0397,0.0000</t>
-  </si>
-  <si>
-    <t>0.8813,0.0038,0.1455,0.0004</t>
-  </si>
-  <si>
-    <t>0.7274,0.0066,0.3986,0.0002</t>
-  </si>
-  <si>
-    <t>0.9268,0.0221,0.0453,0.0001</t>
-  </si>
-  <si>
-    <t>0.8030,0.1420,0.0876,0.0006</t>
-  </si>
-  <si>
-    <t>0.9657,0.0121,0.0145,0.0001</t>
-  </si>
-  <si>
-    <t>0.9092,0.0467,0.0387,0.0003</t>
-  </si>
-  <si>
-    <t>0.9696,0.0104,0.0153,0.0001</t>
-  </si>
-  <si>
-    <t>0.9382,0.0473,0.0241,0.0001</t>
-  </si>
-  <si>
-    <t>0.9307,0.0356,0.0211,0.0002</t>
-  </si>
-  <si>
-    <t>0.8719,0.0395,0.0887,0.0002</t>
-  </si>
-  <si>
-    <t>0.6637,0.2746,0.0728,0.0055</t>
-  </si>
-  <si>
-    <t>0.8550,0.0573,0.0496,0.0044</t>
-  </si>
-  <si>
-    <t>0.7756,0.1027,0.0765,0.0074</t>
-  </si>
-  <si>
-    <t>0.7136,0.0888,0.0696,0.0267</t>
-  </si>
-  <si>
-    <t>0.6698,0.1383,0.0809,0.0171</t>
-  </si>
-  <si>
-    <t>0.9535,0.0140,0.0248,0.0002</t>
-  </si>
-  <si>
-    <t>0.9377,0.0402,0.0232,0.0004</t>
-  </si>
-  <si>
-    <t>0.9619,0.0072,0.0248,0.0002</t>
-  </si>
-  <si>
-    <t>0.9349,0.0031,0.0876,0.0001</t>
-  </si>
-  <si>
-    <t>0.9461,0.0172,0.0198,0.0002</t>
-  </si>
-  <si>
-    <t>0.6912,0.0787,0.2445,0.0020</t>
-  </si>
-  <si>
-    <t>0.9855,0.0013,0.0107,0.0000</t>
-  </si>
-  <si>
-    <t>0.9741,0.0004,0.0272,0.0000</t>
-  </si>
-  <si>
-    <t>0.9501,0.0035,0.0555,0.0001</t>
-  </si>
-  <si>
-    <t>0.9348,0.0053,0.0537,0.0002</t>
-  </si>
-  <si>
-    <t>0.8001,0.0648,0.0409,0.0194</t>
-  </si>
-  <si>
-    <t>0.8910,0.0289,0.0288,0.0061</t>
-  </si>
-  <si>
-    <t>0.7354,0.0963,0.0731,0.0172</t>
-  </si>
-  <si>
-    <t>0.3560,0.6719,0.1194,0.0055</t>
-  </si>
-  <si>
-    <t>0.6786,0.0675,0.0311,0.0423</t>
-  </si>
-  <si>
-    <t>0.7205,0.1094,0.0503,0.0154</t>
-  </si>
-  <si>
-    <t>0.7852,0.1199,0.0425,0.0077</t>
-  </si>
-  <si>
-    <t>0.8692,0.0794,0.0372,0.0022</t>
-  </si>
-  <si>
-    <t>0.7823,0.0365,0.2462,0.0002</t>
-  </si>
-  <si>
-    <t>0.8408,0.0790,0.0658,0.0019</t>
-  </si>
-  <si>
-    <t>0.9150,0.0399,0.0343,0.0012</t>
-  </si>
-  <si>
-    <t>0.8210,0.0022,0.3723,0.0001</t>
-  </si>
-  <si>
-    <t>0.6922,0.0066,0.4264,0.0011</t>
-  </si>
-  <si>
-    <t>0.9315,0.0074,0.0763,0.0002</t>
-  </si>
-  <si>
-    <t>0.6378,0.0045,0.6323,0.0002</t>
-  </si>
-  <si>
-    <t>0.9428,0.0050,0.0602,0.0002</t>
-  </si>
-  <si>
-    <t>0.5633,0.0036,0.6269,0.0003</t>
-  </si>
-  <si>
-    <t>0.9760,0.0010,0.0189,0.0000</t>
-  </si>
-  <si>
-    <t>0.9474,0.0073,0.0349,0.0004</t>
-  </si>
-  <si>
-    <t>0.9567,0.0055,0.0267,0.0004</t>
-  </si>
-  <si>
-    <t>0.9377,0.0118,0.0490,0.0001</t>
-  </si>
-  <si>
-    <t>0.9555,0.0109,0.0194,0.0002</t>
-  </si>
-  <si>
-    <t>0.7274,0.1532,0.0400,0.0072</t>
-  </si>
-  <si>
-    <t>0.7574,0.0909,0.0355,0.0133</t>
-  </si>
-  <si>
-    <t>0.5980,0.3403,0.0550,0.0091</t>
-  </si>
-  <si>
-    <t>0.8434,0.0638,0.0264,0.0084</t>
-  </si>
-  <si>
-    <t>0.8409,0.0392,0.0231,0.0100</t>
-  </si>
-  <si>
-    <t>0.8265,0.0722,0.0451,0.0104</t>
-  </si>
-  <si>
-    <t>0.8334,0.0444,0.0304,0.0146</t>
-  </si>
-  <si>
-    <t>0.6389,0.2244,0.0792,0.0119</t>
-  </si>
-  <si>
-    <t>0.9256,0.0014,0.1404,0.0000</t>
-  </si>
-  <si>
-    <t>0.3991,0.0211,0.7110,0.0003</t>
-  </si>
-  <si>
-    <t>0.8947,0.0027,0.1502,0.0001</t>
-  </si>
-  <si>
-    <t>0.9341,0.0100,0.0563,0.0001</t>
-  </si>
-  <si>
-    <t>0.8812,0.0063,0.1573,0.0004</t>
-  </si>
-  <si>
-    <t>0.9327,0.0189,0.0465,0.0003</t>
-  </si>
-  <si>
-    <t>0.9143,0.0073,0.0870,0.0001</t>
-  </si>
-  <si>
-    <t>0.9623,0.0010,0.0365,0.0001</t>
-  </si>
-  <si>
-    <t>0.8177,0.0636,0.0769,0.0079</t>
-  </si>
-  <si>
-    <t>0.9609,0.0118,0.0110,0.0006</t>
-  </si>
-  <si>
-    <t>0.9402,0.0181,0.0138,0.0022</t>
-  </si>
-  <si>
-    <t>0.9427,0.0063,0.0263,0.0010</t>
-  </si>
-  <si>
-    <t>0.9062,0.0359,0.0236,0.0031</t>
-  </si>
-  <si>
-    <t>0.8929,0.0584,0.0242,0.0014</t>
+    <t>0.8482,0.0119,0.0038,0.1192</t>
+  </si>
+  <si>
+    <t>0.0166,0.0003,0.0007,0.9947</t>
+  </si>
+  <si>
+    <t>0.9720,0.0010,0.0010,0.0171</t>
+  </si>
+  <si>
+    <t>0.0958,0.0047,0.0237,0.9287</t>
+  </si>
+  <si>
+    <t>0.9958,0.0006,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9922,0.0031,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9956,0.0025,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9947,0.0009,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9962,0.0013,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9293,0.0151,0.0412,0.0017</t>
+  </si>
+  <si>
+    <t>0.1916,0.0096,0.8741,0.0003</t>
+  </si>
+  <si>
+    <t>0.2164,0.0081,0.9008,0.0035</t>
+  </si>
+  <si>
+    <t>0.0688,0.0066,0.9569,0.0034</t>
+  </si>
+  <si>
+    <t>0.9622,0.0377,0.0055,0.0017</t>
+  </si>
+  <si>
+    <t>0.0008,0.9981,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.0063,0.9914,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.0620,0.9388,0.0094,0.0013</t>
+  </si>
+  <si>
+    <t>0.0012,0.9970,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.9982,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.8042,0.0025,0.1997,0.0059</t>
+  </si>
+  <si>
+    <t>0.5703,0.0212,0.4643,0.0148</t>
+  </si>
+  <si>
+    <t>0.0061,0.0007,0.9950,0.0015</t>
+  </si>
+  <si>
+    <t>0.4566,0.0092,0.7296,0.0050</t>
+  </si>
+  <si>
+    <t>0.8446,0.0007,0.3000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0601,0.0005,0.9796,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.9919,0.0184</t>
+  </si>
+  <si>
+    <t>0.8565,0.1787,0.0116,0.0011</t>
+  </si>
+  <si>
+    <t>0.7253,0.0971,0.1678,0.0208</t>
+  </si>
+  <si>
+    <t>0.0044,0.0175,0.9896,0.0086</t>
+  </si>
+  <si>
+    <t>0.0011,0.9914,0.0191,0.0002</t>
+  </si>
+  <si>
+    <t>0.8041,0.0772,0.0550,0.0440</t>
+  </si>
+  <si>
+    <t>0.1960,0.0034,0.8934,0.0046</t>
+  </si>
+  <si>
+    <t>0.7146,0.4202,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.0079,0.9851,0.0867,0.0008</t>
+  </si>
+  <si>
+    <t>0.1273,0.4388,0.5520,0.0140</t>
+  </si>
+  <si>
+    <t>0.0274,0.0042,0.9763,0.0030</t>
+  </si>
+  <si>
+    <t>0.1449,0.0119,0.9155,0.0045</t>
+  </si>
+  <si>
+    <t>0.0715,0.0011,0.9433,0.0077</t>
+  </si>
+  <si>
+    <t>0.0056,0.0029,0.9955,0.0003</t>
+  </si>
+  <si>
+    <t>0.0241,0.8689,0.2364,0.0054</t>
+  </si>
+  <si>
+    <t>0.0025,0.0076,0.9890,0.0037</t>
+  </si>
+  <si>
+    <t>0.1345,0.3416,0.0021,0.6192</t>
+  </si>
+  <si>
+    <t>0.0558,0.9343,0.0134,0.0071</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.9953,0.0222,0.0007</t>
+  </si>
+  <si>
+    <t>0.0036,0.0369,0.9746,0.0076</t>
+  </si>
+  <si>
+    <t>0.0053,0.3219,0.9802,0.0021</t>
+  </si>
+  <si>
+    <t>0.0307,0.0029,0.9812,0.0022</t>
+  </si>
+  <si>
+    <t>0.5648,0.0020,0.5945,0.0043</t>
+  </si>
+  <si>
+    <t>0.0036,0.0040,0.9865,0.0113</t>
+  </si>
+  <si>
+    <t>0.0192,0.1994,0.9576,0.0042</t>
+  </si>
+  <si>
+    <t>0.9870,0.0091,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9679,0.0178,0.0103,0.0014</t>
+  </si>
+  <si>
+    <t>0.9622,0.0199,0.0146,0.0022</t>
+  </si>
+  <si>
+    <t>0.0228,0.1184,0.9650,0.0108</t>
+  </si>
+  <si>
+    <t>0.9940,0.0021,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9883,0.0104,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9799,0.0223,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.8879,0.9914,0.0001</t>
+  </si>
+  <si>
+    <t>0.0198,0.1101,0.9657,0.0023</t>
+  </si>
+  <si>
+    <t>0.0050,0.0334,0.9809,0.0070</t>
+  </si>
+  <si>
+    <t>0.0005,0.9586,0.9748,0.0001</t>
+  </si>
+  <si>
+    <t>0.0077,0.0030,0.9934,0.0012</t>
+  </si>
+  <si>
+    <t>0.0875,0.8039,0.0717,0.0050</t>
+  </si>
+  <si>
+    <t>0.0261,0.9708,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.3510,0.0282,0.7941,0.0132</t>
+  </si>
+  <si>
+    <t>0.4634,0.2533,0.4261,0.0111</t>
+  </si>
+  <si>
+    <t>0.0142,0.0074,0.9772,0.0156</t>
+  </si>
+  <si>
+    <t>0.0050,0.8624,0.8099,0.0006</t>
+  </si>
+  <si>
+    <t>0.0029,0.8970,0.7610,0.0007</t>
+  </si>
+  <si>
+    <t>0.0039,0.9908,0.0115,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.8835,0.7591,0.0015</t>
+  </si>
+  <si>
+    <t>0.0429,0.0026,0.0591,0.9225</t>
+  </si>
+  <si>
+    <t>0.0014,0.0008,0.0019,0.9981</t>
+  </si>
+  <si>
+    <t>0.0187,0.0017,0.0003,0.9938</t>
+  </si>
+  <si>
+    <t>0.0080,0.0006,0.0067,0.9927</t>
+  </si>
+  <si>
+    <t>0.0066,0.0149,0.0097,0.9894</t>
+  </si>
+  <si>
+    <t>0.0013,0.0027,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0005,0.9858,0.8803,0.0001</t>
+  </si>
+  <si>
+    <t>0.0481,0.3026,0.8558,0.0020</t>
+  </si>
+  <si>
+    <t>0.0034,0.9575,0.1907,0.0047</t>
+  </si>
+  <si>
+    <t>0.0230,0.0869,0.9516,0.0020</t>
+  </si>
+  <si>
+    <t>0.0015,0.9732,0.8354,0.0003</t>
+  </si>
+  <si>
+    <t>0.0065,0.9681,0.1500,0.0015</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9929,0.0080,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9822,0.0128,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9940,0.0041,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9962,0.0021,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0025,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9916,0.0089,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9730,0.0375,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9944,0.0015,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9969,0.0014,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0014,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9973,0.0003,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.0019,0.9963,0.0052</t>
+  </si>
+  <si>
+    <t>0.0682,0.0021,0.9804,0.0007</t>
+  </si>
+  <si>
+    <t>0.9516,0.0024,0.0136,0.0095</t>
+  </si>
+  <si>
+    <t>0.1467,0.0017,0.9369,0.0013</t>
+  </si>
+  <si>
+    <t>0.0012,0.9966,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.0025,0.9952,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.0117,0.9826,0.0016,0.0019</t>
+  </si>
+  <si>
+    <t>0.0129,0.9779,0.0025,0.0028</t>
+  </si>
+  <si>
+    <t>0.0005,0.9986,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.9938,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.1844,0.8694,0.0045,0.0011</t>
+  </si>
+  <si>
+    <t>0.8131,0.0174,0.1842,0.0034</t>
+  </si>
+  <si>
+    <t>0.1838,0.0018,0.9271,0.0005</t>
+  </si>
+  <si>
+    <t>0.3401,0.0202,0.6218,0.0889</t>
+  </si>
+  <si>
+    <t>0.4084,0.0398,0.5868,0.0091</t>
+  </si>
+  <si>
+    <t>0.0882,0.3623,0.0538,0.6646</t>
+  </si>
+  <si>
+    <t>0.0174,0.9713,0.0694,0.0007</t>
+  </si>
+  <si>
+    <t>0.0041,0.9875,0.0074,0.0026</t>
+  </si>
+  <si>
+    <t>0.0008,0.9972,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.0051,0.9635,0.5565,0.0010</t>
+  </si>
+  <si>
+    <t>0.0087,0.9904,0.0188,0.0001</t>
+  </si>
+  <si>
+    <t>0.8835,0.1223,0.0179,0.0032</t>
+  </si>
+  <si>
+    <t>0.9805,0.0148,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.9854,0.0078,0.0012,0.0021</t>
+  </si>
+  <si>
+    <t>0.9951,0.0005,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9866,0.0020,0.0048,0.0023</t>
+  </si>
+  <si>
+    <t>0.9935,0.0022,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9921,0.0024,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9880,0.0014,0.0015,0.0038</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0080,0.1301,0.9642,0.0017</t>
+  </si>
+  <si>
+    <t>0.0018,0.8607,0.9403,0.0003</t>
+  </si>
+  <si>
+    <t>0.0300,0.2860,0.8030,0.0014</t>
+  </si>
+  <si>
+    <t>0.1058,0.0114,0.9284,0.0023</t>
+  </si>
+  <si>
+    <t>0.9849,0.0040,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.8417,0.0056,0.1972,0.0014</t>
+  </si>
+  <si>
+    <t>0.3037,0.0015,0.8223,0.0088</t>
+  </si>
+  <si>
+    <t>0.8909,0.0079,0.1145,0.0006</t>
+  </si>
+  <si>
+    <t>0.0464,0.0069,0.0169,0.9618</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0023,0.9990</t>
+  </si>
+  <si>
+    <t>0.0068,0.0037,0.0042,0.9942</t>
+  </si>
+  <si>
+    <t>0.0027,0.0008,0.0009,0.9981</t>
+  </si>
+  <si>
+    <t>0.0008,0.5319,0.9620,0.0024</t>
+  </si>
+  <si>
+    <t>0.9931,0.0021,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.2921,0.7737,0.0023,0.0037</t>
+  </si>
+  <si>
+    <t>0.9773,0.0087,0.0051,0.0073</t>
+  </si>
+  <si>
+    <t>0.5823,0.4953,0.0062,0.0038</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.7531,0.0064,0.0197,0.2721</t>
+  </si>
+  <si>
+    <t>0.9914,0.0012,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.0047,0.4600,0.9201,0.0400</t>
+  </si>
+  <si>
+    <t>0.9556,0.0009,0.0010,0.0489</t>
+  </si>
+  <si>
+    <t>0.9532,0.0068,0.0031,0.0266</t>
+  </si>
+  <si>
+    <t>0.4460,0.5861,0.0176,0.0064</t>
+  </si>
+  <si>
+    <t>0.9547,0.0354,0.0073,0.0012</t>
+  </si>
+  <si>
+    <t>0.9781,0.0068,0.0094,0.0012</t>
+  </si>
+  <si>
+    <t>0.5531,0.3945,0.0480,0.0138</t>
+  </si>
+  <si>
+    <t>0.9439,0.0263,0.0166,0.0013</t>
+  </si>
+  <si>
+    <t>0.9932,0.0027,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9847,0.0028,0.0018,0.0051</t>
+  </si>
+  <si>
+    <t>0.9965,0.0003,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9949,0.0009,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9920,0.0007,0.0003,0.0046</t>
+  </si>
+  <si>
+    <t>0.9955,0.0013,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9892,0.0033,0.0020,0.0029</t>
+  </si>
+  <si>
+    <t>0.9952,0.0008,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.8290,0.1276,0.0045,0.0133</t>
+  </si>
+  <si>
+    <t>0.8457,0.2037,0.0067,0.0015</t>
+  </si>
+  <si>
+    <t>0.9115,0.1002,0.0110,0.0020</t>
+  </si>
+  <si>
+    <t>0.0294,0.0836,0.9777,0.0015</t>
+  </si>
+  <si>
+    <t>0.9952,0.0018,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9800,0.0142,0.0025,0.0012</t>
+  </si>
+  <si>
+    <t>0.9680,0.0255,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9810,0.0088,0.0020,0.0044</t>
+  </si>
+  <si>
+    <t>0.0100,0.0028,0.9963,0.0004</t>
+  </si>
+  <si>
+    <t>0.9543,0.0406,0.0087,0.0039</t>
+  </si>
+  <si>
+    <t>0.0168,0.0089,0.9769,0.0071</t>
+  </si>
+  <si>
+    <t>0.0243,0.0263,0.9652,0.0124</t>
+  </si>
+  <si>
+    <t>0.0259,0.0016,0.9866,0.0021</t>
+  </si>
+  <si>
+    <t>0.0023,0.0226,0.9920,0.0033</t>
+  </si>
+  <si>
+    <t>0.0213,0.0056,0.9863,0.0008</t>
+  </si>
+  <si>
+    <t>0.0302,0.0025,0.9816,0.0022</t>
+  </si>
+  <si>
+    <t>0.0017,0.0016,0.9968,0.0018</t>
+  </si>
+  <si>
+    <t>0.0764,0.0311,0.9105,0.0227</t>
+  </si>
+  <si>
+    <t>0.0883,0.0112,0.9254,0.0015</t>
+  </si>
+  <si>
+    <t>0.2505,0.0148,0.8175,0.0082</t>
+  </si>
+  <si>
+    <t>0.3441,0.0237,0.7282,0.0024</t>
+  </si>
+  <si>
+    <t>0.1410,0.0915,0.7693,0.0043</t>
+  </si>
+  <si>
+    <t>0.8687,0.0053,0.1835,0.0003</t>
+  </si>
+  <si>
+    <t>0.8337,0.0624,0.0696,0.0056</t>
+  </si>
+  <si>
+    <t>0.0199,0.0031,0.9889,0.0021</t>
+  </si>
+  <si>
+    <t>0.0449,0.9604,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0088,0.9910,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.6874,0.5036,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9935,0.0082,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.4194,0.6713,0.0051,0.0034</t>
+  </si>
+  <si>
+    <t>0.8214,0.1195,0.0343,0.0027</t>
+  </si>
+  <si>
+    <t>0.9858,0.0012,0.0037,0.0019</t>
+  </si>
+  <si>
+    <t>0.8707,0.0075,0.0566,0.0186</t>
+  </si>
+  <si>
+    <t>0.7411,0.0042,0.4135,0.0015</t>
+  </si>
+  <si>
+    <t>0.8291,0.0124,0.1045,0.0096</t>
+  </si>
+  <si>
+    <t>0.0172,0.0035,0.9683,0.0560</t>
+  </si>
+  <si>
+    <t>0.1373,0.0700,0.8670,0.0171</t>
+  </si>
+  <si>
+    <t>0.2840,0.0214,0.6628,0.0645</t>
+  </si>
+  <si>
+    <t>0.1213,0.0075,0.8871,0.0081</t>
+  </si>
+  <si>
+    <t>0.0126,0.0693,0.9573,0.0054</t>
+  </si>
+  <si>
+    <t>0.9933,0.0009,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9612,0.0279,0.0027,0.0060</t>
+  </si>
+  <si>
+    <t>0.9701,0.0296,0.0022,0.0030</t>
+  </si>
+  <si>
+    <t>0.9870,0.0041,0.0014,0.0038</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9932,0.0022,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0340,0.0013,0.9931,0.0003</t>
+  </si>
+  <si>
+    <t>0.2360,0.0736,0.7795,0.0249</t>
+  </si>
+  <si>
+    <t>0.9445,0.0201,0.0233,0.0084</t>
+  </si>
+  <si>
+    <t>0.0296,0.0025,0.9839,0.0015</t>
+  </si>
+  <si>
+    <t>0.0122,0.0066,0.9640,0.0308</t>
+  </si>
+  <si>
+    <t>0.0146,0.0966,0.9542,0.0093</t>
+  </si>
+  <si>
+    <t>0.0040,0.0028,0.9952,0.0008</t>
+  </si>
+  <si>
+    <t>0.0350,0.0066,0.9598,0.0085</t>
+  </si>
+  <si>
+    <t>0.0134,0.0098,0.9904,0.0007</t>
+  </si>
+  <si>
+    <t>0.0120,0.0101,0.9864,0.0026</t>
+  </si>
+  <si>
+    <t>0.0209,0.0276,0.9567,0.0013</t>
+  </si>
+  <si>
+    <t>0.7483,0.0026,0.3443,0.0053</t>
+  </si>
+  <si>
+    <t>0.8671,0.0040,0.1702,0.0048</t>
+  </si>
+  <si>
+    <t>0.9905,0.0015,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9905,0.0083,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9898,0.0042,0.0026,0.0008</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0021,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0012,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9937,0.0047,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9970,0.0012,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0225,0.0376,0.9581,0.0049</t>
+  </si>
+  <si>
+    <t>0.0032,0.1542,0.9828,0.0009</t>
+  </si>
+  <si>
+    <t>0.0076,0.0145,0.9823,0.0046</t>
+  </si>
+  <si>
+    <t>0.2120,0.0355,0.7517,0.0141</t>
+  </si>
+  <si>
+    <t>0.0170,0.0037,0.9864,0.0013</t>
+  </si>
+  <si>
+    <t>0.0610,0.0022,0.7692,0.1817</t>
+  </si>
+  <si>
+    <t>0.0261,0.0064,0.9835,0.0013</t>
+  </si>
+  <si>
+    <t>0.0651,0.0077,0.6072,0.2632</t>
+  </si>
+  <si>
+    <t>0.9257,0.0009,0.0042,0.0534</t>
+  </si>
+  <si>
+    <t>0.0356,0.0081,0.0012,0.9835</t>
+  </si>
+  <si>
+    <t>0.0101,0.0001,0.0024,0.9933</t>
+  </si>
+  <si>
+    <t>0.0058,0.0011,0.0058,0.9939</t>
+  </si>
+  <si>
+    <t>0.0036,0.0001,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.9057,0.0270,0.0069,0.0324</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -4949,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="C216" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D216" t="s">
         <v>478</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
